--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-device|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-device|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -382,7 +382,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -481,7 +481,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-device|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-device|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Device.meta.security</t>
@@ -649,7 +649,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1688,7 +1688,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-device.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
